--- a/public/results/2024/Bottoms Up 2024 League Stats - Week 22.xlsx
+++ b/public/results/2024/Bottoms Up 2024 League Stats - Week 22.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28025"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mark\source\repos\golf-league-site\public\results\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/mthutter/CODE/golf-league-site/public/results/2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9AEB79EC-5047-4EC5-A632-E542B22DD17B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{31053A6D-5211-B245-9110-CBE422AD4C96}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3120" yWindow="1290" windowWidth="21945" windowHeight="14910" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3120" yWindow="1300" windowWidth="21940" windowHeight="14920" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Template" sheetId="14" r:id="rId1"/>
@@ -1918,6 +1918,15 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="14" fontId="14" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1929,63 +1938,6 @@
     </xf>
     <xf numFmtId="14" fontId="15" fillId="0" borderId="25" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="14" fontId="19" fillId="0" borderId="22" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2031,6 +1983,54 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="21" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="28" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="9" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="1" fontId="14" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="15" fillId="0" borderId="49" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="45" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2511,25 +2511,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{75685173-5684-4D7E-8458-1B841D06EDCF}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="23" style="3" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="8.140625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="7.5703125" style="3" customWidth="1"/>
-    <col min="15" max="15" width="17.140625" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="8.1640625" style="3" customWidth="1"/>
+    <col min="14" max="14" width="7.5" style="3" customWidth="1"/>
+    <col min="15" max="15" width="17.1640625" style="3" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -2559,7 +2559,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -2589,7 +2589,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -2617,7 +2617,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -2677,7 +2677,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -2730,7 +2730,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -2778,7 +2778,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12"/>
       <c r="B7" s="13" t="s">
         <v>73</v>
@@ -2814,7 +2814,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -2876,7 +2876,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12"/>
       <c r="B9" s="13"/>
       <c r="C9" s="13"/>
@@ -2903,7 +2903,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17" t="str">
@@ -2957,7 +2957,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12"/>
       <c r="B11" s="13"/>
       <c r="C11" s="13"/>
@@ -2985,7 +2985,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17" t="str">
@@ -3040,7 +3040,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12"/>
       <c r="B13" s="13"/>
       <c r="C13" s="13"/>
@@ -3068,7 +3068,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17" t="str">
@@ -3123,7 +3123,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12"/>
       <c r="B15" s="13"/>
       <c r="C15" s="13"/>
@@ -3154,7 +3154,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17" t="str">
@@ -3212,7 +3212,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12"/>
       <c r="B17" s="13"/>
       <c r="C17" s="13"/>
@@ -3243,7 +3243,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17" t="str">
@@ -3301,7 +3301,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12"/>
       <c r="B19" s="13"/>
       <c r="C19" s="13"/>
@@ -3328,7 +3328,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17" t="str">
@@ -3382,7 +3382,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -3408,25 +3408,25 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{41446D83-F516-465D-9CB3-F2ACFB898189}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -3456,7 +3456,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -3486,7 +3486,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -3514,7 +3514,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -3574,7 +3574,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -3627,7 +3627,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -3675,7 +3675,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="43" t="s">
         <v>50</v>
       </c>
@@ -3733,7 +3733,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -3795,7 +3795,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="43" t="s">
         <v>66</v>
       </c>
@@ -3844,7 +3844,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -3898,7 +3898,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="43" t="s">
         <v>52</v>
       </c>
@@ -3948,7 +3948,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -4003,7 +4003,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="43" t="s">
         <v>54</v>
       </c>
@@ -4053,7 +4053,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -4108,7 +4108,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="43" t="s">
         <v>56</v>
       </c>
@@ -4161,7 +4161,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -4219,7 +4219,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>64</v>
       </c>
@@ -4272,7 +4272,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -4330,7 +4330,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="43" t="s">
         <v>51</v>
       </c>
@@ -4379,7 +4379,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -4433,7 +4433,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -4456,25 +4456,25 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6646222A-4073-4508-A79B-C97E9BFB6981}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="15" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -4504,7 +4504,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -4534,7 +4534,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -4562,7 +4562,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -4622,7 +4622,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -4675,7 +4675,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -4723,7 +4723,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>62</v>
       </c>
@@ -4781,7 +4781,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -4843,7 +4843,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>66</v>
       </c>
@@ -4892,7 +4892,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -4946,7 +4946,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>54</v>
       </c>
@@ -4996,7 +4996,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -5051,7 +5051,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>55</v>
       </c>
@@ -5101,7 +5101,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -5156,7 +5156,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>52</v>
       </c>
@@ -5209,7 +5209,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -5267,7 +5267,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>63</v>
       </c>
@@ -5317,7 +5317,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -5375,7 +5375,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
@@ -5424,7 +5424,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -5478,7 +5478,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -5501,25 +5501,25 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C9469CDA-F232-4470-AA18-D25AE87FB336}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="15" style="3" customWidth="1"/>
     <col min="2" max="2" width="12" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -5549,7 +5549,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -5579,7 +5579,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -5607,7 +5607,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -5667,7 +5667,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -5720,7 +5720,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -5768,7 +5768,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>64</v>
       </c>
@@ -5826,7 +5826,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -5888,7 +5888,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>94</v>
       </c>
@@ -5934,7 +5934,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -5958,7 +5958,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>56</v>
       </c>
@@ -6008,7 +6008,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -6063,7 +6063,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>53</v>
       </c>
@@ -6113,7 +6113,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -6168,7 +6168,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>50</v>
       </c>
@@ -6221,7 +6221,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -6279,7 +6279,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>67</v>
       </c>
@@ -6329,7 +6329,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -6387,7 +6387,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>54</v>
       </c>
@@ -6436,7 +6436,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -6490,7 +6490,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>52</v>
       </c>
@@ -6543,7 +6543,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -6601,7 +6601,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>63</v>
       </c>
@@ -6651,7 +6651,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -6709,7 +6709,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>55</v>
       </c>
@@ -6758,7 +6758,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -6812,7 +6812,7 @@
       <c r="R26" s="39"/>
       <c r="T26" s="3"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>62</v>
       </c>
@@ -6861,7 +6861,7 @@
       <c r="R27" s="39"/>
       <c r="T27" s="3"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17">
@@ -6931,25 +6931,25 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F22E4CC9-F2D4-4C19-8020-991DDE667A2D}">
   <dimension ref="A1:Z21"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="16.42578125" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="16.5" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -6979,7 +6979,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -7009,7 +7009,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -7037,7 +7037,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -7097,7 +7097,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -7150,7 +7150,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -7198,7 +7198,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -7256,7 +7256,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -7318,7 +7318,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>53</v>
       </c>
@@ -7367,7 +7367,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -7421,7 +7421,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -7471,7 +7471,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -7526,7 +7526,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>54</v>
       </c>
@@ -7576,7 +7576,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -7631,7 +7631,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>63</v>
       </c>
@@ -7684,7 +7684,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -7742,7 +7742,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>52</v>
       </c>
@@ -7792,7 +7792,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -7850,7 +7850,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
@@ -7899,7 +7899,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -7953,7 +7953,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E21" s="34"/>
       <c r="G21" s="34"/>
       <c r="H21" s="34"/>
@@ -7976,25 +7976,25 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3C9E60FC-448D-4530-A619-75ED12DD2F32}">
   <dimension ref="A1:Z19"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -8024,7 +8024,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -8054,7 +8054,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -8082,7 +8082,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -8144,7 +8144,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -8197,7 +8197,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -8245,7 +8245,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -8303,7 +8303,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -8365,7 +8365,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>52</v>
       </c>
@@ -8414,7 +8414,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -8468,7 +8468,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>53</v>
       </c>
@@ -8518,7 +8518,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -8573,7 +8573,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>54</v>
       </c>
@@ -8623,7 +8623,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -8678,7 +8678,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>55</v>
       </c>
@@ -8731,7 +8731,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -8789,7 +8789,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -8839,7 +8839,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -8897,7 +8897,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E19" s="34"/>
       <c r="G19" s="34"/>
       <c r="H19" s="34"/>
@@ -8920,25 +8920,25 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00F5C281-981B-5047-AD15-5610AC69ACF4}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -8968,7 +8968,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -8998,7 +8998,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -9026,7 +9026,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -9086,7 +9086,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -9139,7 +9139,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -9187,7 +9187,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>52</v>
       </c>
@@ -9245,7 +9245,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -9307,7 +9307,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>55</v>
       </c>
@@ -9356,7 +9356,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -9410,7 +9410,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -9460,7 +9460,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -9515,7 +9515,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>68</v>
       </c>
@@ -9563,7 +9563,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -9616,7 +9616,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -9669,7 +9669,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -9727,7 +9727,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>53</v>
       </c>
@@ -9780,7 +9780,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -9838,7 +9838,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>100</v>
       </c>
@@ -9887,7 +9887,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -9941,7 +9941,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -9994,7 +9994,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -10052,7 +10052,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>64</v>
       </c>
@@ -10105,7 +10105,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -10163,7 +10163,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
@@ -10212,7 +10212,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -10281,25 +10281,25 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6306ACE2-8B06-415D-A9B7-58C4F90B35BE}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -10329,7 +10329,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -10359,7 +10359,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -10387,7 +10387,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -10447,7 +10447,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -10500,7 +10500,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -10548,7 +10548,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>53</v>
       </c>
@@ -10606,7 +10606,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -10668,7 +10668,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>100</v>
       </c>
@@ -10717,7 +10717,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -10771,7 +10771,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>62</v>
       </c>
@@ -10821,7 +10821,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -10876,7 +10876,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>51</v>
       </c>
@@ -10926,7 +10926,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -10981,7 +10981,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>63</v>
       </c>
@@ -11034,7 +11034,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -11092,7 +11092,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>54</v>
       </c>
@@ -11145,7 +11145,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -11203,7 +11203,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>55</v>
       </c>
@@ -11252,7 +11252,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -11306,7 +11306,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>52</v>
       </c>
@@ -11359,7 +11359,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -11417,7 +11417,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>66</v>
       </c>
@@ -11470,7 +11470,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -11528,7 +11528,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>56</v>
       </c>
@@ -11577,7 +11577,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -11646,12 +11646,12 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95AF07A2-A4D8-47C9-8AEF-3807C17C24E0}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="14.140625" style="3"/>
+    <col min="1" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="210" t="s">
         <v>117</v>
       </c>
@@ -11659,13 +11659,13 @@
       <c r="C1" s="210"/>
       <c r="D1" s="210"/>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="210"/>
       <c r="B2" s="210"/>
       <c r="C2" s="210"/>
       <c r="D2" s="210"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="210"/>
       <c r="B3" s="210"/>
       <c r="C3" s="210"/>
@@ -11682,25 +11682,25 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A383DFD8-EF94-43AD-B369-F6382E54D9D0}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -11730,7 +11730,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -11760,7 +11760,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -11788,7 +11788,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -11848,7 +11848,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -11901,7 +11901,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -11949,7 +11949,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>54</v>
       </c>
@@ -12007,7 +12007,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -12069,7 +12069,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>55</v>
       </c>
@@ -12118,7 +12118,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -12172,7 +12172,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -12222,7 +12222,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -12277,7 +12277,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>67</v>
       </c>
@@ -12327,7 +12327,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -12382,7 +12382,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>63</v>
       </c>
@@ -12435,7 +12435,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -12493,7 +12493,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>62</v>
       </c>
@@ -12546,7 +12546,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -12604,7 +12604,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>53</v>
       </c>
@@ -12653,7 +12653,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -12707,7 +12707,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>100</v>
       </c>
@@ -12760,7 +12760,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -12818,7 +12818,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>52</v>
       </c>
@@ -12871,7 +12871,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -12929,7 +12929,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>51</v>
       </c>
@@ -12978,7 +12978,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -13047,12 +13047,12 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{067A617B-B8E0-4C9B-B7E7-8E356D2972A9}">
   <dimension ref="A1:D3"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="16384" width="14.140625" style="3"/>
+    <col min="1" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="210" t="s">
         <v>117</v>
       </c>
@@ -13060,13 +13060,13 @@
       <c r="C1" s="210"/>
       <c r="D1" s="210"/>
     </row>
-    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A2" s="210"/>
       <c r="B2" s="210"/>
       <c r="C2" s="210"/>
       <c r="D2" s="210"/>
     </row>
-    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:4" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A3" s="210"/>
       <c r="B3" s="210"/>
       <c r="C3" s="210"/>
@@ -13083,297 +13083,297 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6A1EE897-404D-4ADC-856A-1E864FE4E3AA}">
   <dimension ref="A1:BH26"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="9.1640625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="7.7109375" customWidth="1"/>
+    <col min="1" max="1" width="7.6640625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
-    <col min="3" max="3" width="4.140625" customWidth="1"/>
-    <col min="4" max="4" width="12.28515625" customWidth="1"/>
-    <col min="5" max="5" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="3" max="3" width="4.1640625" customWidth="1"/>
+    <col min="4" max="4" width="12.33203125" customWidth="1"/>
+    <col min="5" max="5" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="6" hidden="1" customWidth="1"/>
-    <col min="7" max="7" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="7" max="7" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="8" max="8" width="6" hidden="1" customWidth="1"/>
-    <col min="9" max="9" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="9" max="9" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="10" max="10" width="6" hidden="1" customWidth="1"/>
-    <col min="11" max="11" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="11" max="11" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="12" max="12" width="6" hidden="1" customWidth="1"/>
-    <col min="13" max="13" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="13" max="13" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="14" max="14" width="6" hidden="1" customWidth="1"/>
-    <col min="15" max="15" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="15" max="15" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="16" max="16" width="6" hidden="1" customWidth="1"/>
-    <col min="17" max="17" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="17" max="17" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="18" max="18" width="6" hidden="1" customWidth="1"/>
-    <col min="19" max="19" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="19" max="19" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="20" max="20" width="6" hidden="1" customWidth="1"/>
-    <col min="21" max="21" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="21" max="21" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="22" max="22" width="6" hidden="1" customWidth="1"/>
-    <col min="23" max="23" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="23" max="23" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="24" max="24" width="6" hidden="1" customWidth="1"/>
-    <col min="25" max="25" width="5.7109375" hidden="1" customWidth="1"/>
+    <col min="25" max="25" width="5.6640625" hidden="1" customWidth="1"/>
     <col min="26" max="26" width="6" hidden="1" customWidth="1"/>
-    <col min="27" max="44" width="7.42578125" hidden="1" customWidth="1"/>
-    <col min="45" max="48" width="7.42578125" customWidth="1"/>
-    <col min="49" max="49" width="7.140625" customWidth="1"/>
-    <col min="50" max="50" width="9.140625" style="86"/>
-    <col min="51" max="51" width="9.140625" style="86" hidden="1" customWidth="1"/>
-    <col min="52" max="52" width="9.140625" hidden="1" customWidth="1"/>
-    <col min="53" max="53" width="8.5703125" hidden="1" customWidth="1"/>
-    <col min="54" max="54" width="7.7109375" hidden="1" customWidth="1"/>
-    <col min="55" max="55" width="13.140625" hidden="1" customWidth="1"/>
-    <col min="56" max="56" width="12.7109375" style="104" hidden="1" customWidth="1"/>
-    <col min="57" max="57" width="8.5703125" customWidth="1"/>
-    <col min="58" max="58" width="6.85546875" customWidth="1"/>
-    <col min="59" max="59" width="8.5703125" customWidth="1"/>
-    <col min="60" max="60" width="10.7109375" customWidth="1"/>
+    <col min="27" max="44" width="7.5" hidden="1" customWidth="1"/>
+    <col min="45" max="48" width="7.5" customWidth="1"/>
+    <col min="49" max="49" width="7.1640625" customWidth="1"/>
+    <col min="50" max="50" width="9.1640625" style="86"/>
+    <col min="51" max="51" width="9.1640625" style="86" hidden="1" customWidth="1"/>
+    <col min="52" max="52" width="9.1640625" hidden="1" customWidth="1"/>
+    <col min="53" max="53" width="8.5" hidden="1" customWidth="1"/>
+    <col min="54" max="54" width="7.6640625" hidden="1" customWidth="1"/>
+    <col min="55" max="55" width="13.1640625" hidden="1" customWidth="1"/>
+    <col min="56" max="56" width="12.6640625" style="104" hidden="1" customWidth="1"/>
+    <col min="57" max="57" width="8.5" customWidth="1"/>
+    <col min="58" max="58" width="6.83203125" customWidth="1"/>
+    <col min="59" max="59" width="8.5" customWidth="1"/>
+    <col min="60" max="60" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:60" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="175" t="s">
+    <row r="1" spans="1:60" s="1" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="194" t="s">
         <v>33</v>
       </c>
-      <c r="B1" s="176"/>
-      <c r="C1" s="181"/>
-      <c r="D1" s="184" t="s">
+      <c r="B1" s="195"/>
+      <c r="C1" s="200"/>
+      <c r="D1" s="203" t="s">
         <v>85</v>
       </c>
-      <c r="E1" s="169" t="s">
+      <c r="E1" s="172" t="s">
         <v>37</v>
       </c>
-      <c r="F1" s="170"/>
-      <c r="G1" s="169" t="s">
+      <c r="F1" s="173"/>
+      <c r="G1" s="172" t="s">
         <v>38</v>
       </c>
-      <c r="H1" s="170"/>
-      <c r="I1" s="169" t="s">
+      <c r="H1" s="173"/>
+      <c r="I1" s="172" t="s">
         <v>39</v>
       </c>
-      <c r="J1" s="170"/>
-      <c r="K1" s="169" t="s">
+      <c r="J1" s="173"/>
+      <c r="K1" s="172" t="s">
         <v>40</v>
       </c>
-      <c r="L1" s="170"/>
-      <c r="M1" s="169" t="s">
+      <c r="L1" s="173"/>
+      <c r="M1" s="172" t="s">
         <v>70</v>
       </c>
-      <c r="N1" s="170"/>
-      <c r="O1" s="169" t="s">
+      <c r="N1" s="173"/>
+      <c r="O1" s="172" t="s">
         <v>84</v>
       </c>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="169" t="s">
+      <c r="P1" s="173"/>
+      <c r="Q1" s="172" t="s">
         <v>89</v>
       </c>
-      <c r="R1" s="170"/>
-      <c r="S1" s="169" t="s">
+      <c r="R1" s="173"/>
+      <c r="S1" s="172" t="s">
         <v>90</v>
       </c>
-      <c r="T1" s="170"/>
-      <c r="U1" s="169" t="s">
+      <c r="T1" s="173"/>
+      <c r="U1" s="172" t="s">
         <v>93</v>
       </c>
-      <c r="V1" s="170"/>
-      <c r="W1" s="169" t="s">
+      <c r="V1" s="173"/>
+      <c r="W1" s="172" t="s">
         <v>95</v>
       </c>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="169" t="s">
+      <c r="X1" s="173"/>
+      <c r="Y1" s="172" t="s">
         <v>96</v>
       </c>
-      <c r="Z1" s="170"/>
-      <c r="AA1" s="169" t="s">
+      <c r="Z1" s="173"/>
+      <c r="AA1" s="172" t="s">
         <v>105</v>
       </c>
-      <c r="AB1" s="170"/>
-      <c r="AC1" s="169" t="s">
+      <c r="AB1" s="173"/>
+      <c r="AC1" s="172" t="s">
         <v>110</v>
       </c>
-      <c r="AD1" s="170"/>
-      <c r="AE1" s="169" t="s">
+      <c r="AD1" s="173"/>
+      <c r="AE1" s="172" t="s">
         <v>112</v>
       </c>
-      <c r="AF1" s="170"/>
-      <c r="AG1" s="169" t="s">
+      <c r="AF1" s="173"/>
+      <c r="AG1" s="172" t="s">
         <v>113</v>
       </c>
-      <c r="AH1" s="170"/>
-      <c r="AI1" s="169" t="s">
+      <c r="AH1" s="173"/>
+      <c r="AI1" s="172" t="s">
         <v>115</v>
       </c>
-      <c r="AJ1" s="170"/>
-      <c r="AK1" s="169" t="s">
+      <c r="AJ1" s="173"/>
+      <c r="AK1" s="172" t="s">
         <v>116</v>
       </c>
-      <c r="AL1" s="170"/>
-      <c r="AM1" s="169" t="s">
+      <c r="AL1" s="173"/>
+      <c r="AM1" s="172" t="s">
         <v>118</v>
       </c>
-      <c r="AN1" s="170"/>
-      <c r="AO1" s="169" t="s">
+      <c r="AN1" s="173"/>
+      <c r="AO1" s="172" t="s">
         <v>119</v>
       </c>
-      <c r="AP1" s="170"/>
-      <c r="AQ1" s="169" t="s">
+      <c r="AP1" s="173"/>
+      <c r="AQ1" s="172" t="s">
         <v>120</v>
       </c>
-      <c r="AR1" s="170"/>
-      <c r="AS1" s="169" t="s">
+      <c r="AR1" s="173"/>
+      <c r="AS1" s="172" t="s">
         <v>124</v>
       </c>
-      <c r="AT1" s="170"/>
-      <c r="AU1" s="169" t="s">
+      <c r="AT1" s="173"/>
+      <c r="AU1" s="172" t="s">
         <v>125</v>
       </c>
-      <c r="AV1" s="170"/>
-      <c r="AW1" s="186" t="s">
+      <c r="AV1" s="173"/>
+      <c r="AW1" s="191" t="s">
         <v>35</v>
       </c>
-      <c r="AX1" s="195" t="s">
+      <c r="AX1" s="179" t="s">
         <v>111</v>
       </c>
       <c r="AY1" s="106"/>
-      <c r="AZ1" s="198" t="s">
+      <c r="AZ1" s="182" t="s">
         <v>103</v>
       </c>
-      <c r="BA1" s="199"/>
-      <c r="BB1" s="199"/>
-      <c r="BC1" s="200"/>
-      <c r="BD1" s="189" t="s">
+      <c r="BA1" s="183"/>
+      <c r="BB1" s="183"/>
+      <c r="BC1" s="184"/>
+      <c r="BD1" s="169" t="s">
         <v>109</v>
       </c>
-      <c r="BE1" s="192" t="s">
+      <c r="BE1" s="176" t="s">
         <v>104</v>
       </c>
-      <c r="BF1" s="193"/>
-      <c r="BG1" s="193"/>
-      <c r="BH1" s="194"/>
-    </row>
-    <row r="2" spans="1:60" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="177"/>
-      <c r="B2" s="178"/>
-      <c r="C2" s="182"/>
-      <c r="D2" s="185"/>
-      <c r="E2" s="171">
+      <c r="BF1" s="177"/>
+      <c r="BG1" s="177"/>
+      <c r="BH1" s="178"/>
+    </row>
+    <row r="2" spans="1:60" s="1" customFormat="1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="196"/>
+      <c r="B2" s="197"/>
+      <c r="C2" s="201"/>
+      <c r="D2" s="204"/>
+      <c r="E2" s="174">
         <v>45418</v>
       </c>
-      <c r="F2" s="172"/>
-      <c r="G2" s="173">
+      <c r="F2" s="175"/>
+      <c r="G2" s="205">
         <v>45425</v>
       </c>
-      <c r="H2" s="174"/>
-      <c r="I2" s="173">
+      <c r="H2" s="206"/>
+      <c r="I2" s="205">
         <v>45432</v>
       </c>
-      <c r="J2" s="174"/>
-      <c r="K2" s="173">
+      <c r="J2" s="206"/>
+      <c r="K2" s="205">
         <v>45439</v>
       </c>
-      <c r="L2" s="174"/>
-      <c r="M2" s="173">
+      <c r="L2" s="206"/>
+      <c r="M2" s="205">
         <v>45446</v>
       </c>
-      <c r="N2" s="174"/>
-      <c r="O2" s="173">
+      <c r="N2" s="206"/>
+      <c r="O2" s="205">
         <v>45453</v>
       </c>
-      <c r="P2" s="174"/>
-      <c r="Q2" s="173">
+      <c r="P2" s="206"/>
+      <c r="Q2" s="205">
         <v>45460</v>
       </c>
-      <c r="R2" s="174"/>
-      <c r="S2" s="173">
+      <c r="R2" s="206"/>
+      <c r="S2" s="205">
         <v>45467</v>
       </c>
-      <c r="T2" s="174"/>
-      <c r="U2" s="173">
+      <c r="T2" s="206"/>
+      <c r="U2" s="205">
         <v>45474</v>
       </c>
-      <c r="V2" s="174"/>
-      <c r="W2" s="173">
+      <c r="V2" s="206"/>
+      <c r="W2" s="205">
         <v>45481</v>
       </c>
-      <c r="X2" s="174"/>
-      <c r="Y2" s="173">
+      <c r="X2" s="206"/>
+      <c r="Y2" s="205">
         <v>45488</v>
       </c>
-      <c r="Z2" s="174"/>
-      <c r="AA2" s="171">
+      <c r="Z2" s="206"/>
+      <c r="AA2" s="174">
         <v>45495</v>
       </c>
-      <c r="AB2" s="172"/>
-      <c r="AC2" s="171">
+      <c r="AB2" s="175"/>
+      <c r="AC2" s="174">
         <v>45502</v>
       </c>
-      <c r="AD2" s="172"/>
-      <c r="AE2" s="171">
+      <c r="AD2" s="175"/>
+      <c r="AE2" s="174">
         <v>45509</v>
       </c>
-      <c r="AF2" s="172"/>
-      <c r="AG2" s="171">
+      <c r="AF2" s="175"/>
+      <c r="AG2" s="174">
         <v>45516</v>
       </c>
-      <c r="AH2" s="172"/>
-      <c r="AI2" s="171">
+      <c r="AH2" s="175"/>
+      <c r="AI2" s="174">
         <v>45523</v>
       </c>
-      <c r="AJ2" s="172"/>
-      <c r="AK2" s="171">
+      <c r="AJ2" s="175"/>
+      <c r="AK2" s="174">
         <v>45530</v>
       </c>
-      <c r="AL2" s="172"/>
-      <c r="AM2" s="171">
+      <c r="AL2" s="175"/>
+      <c r="AM2" s="174">
         <v>45537</v>
       </c>
-      <c r="AN2" s="172"/>
-      <c r="AO2" s="171">
+      <c r="AN2" s="175"/>
+      <c r="AO2" s="174">
         <v>45544</v>
       </c>
-      <c r="AP2" s="172"/>
-      <c r="AQ2" s="171">
+      <c r="AP2" s="175"/>
+      <c r="AQ2" s="174">
         <v>45551</v>
       </c>
-      <c r="AR2" s="172"/>
-      <c r="AS2" s="171">
+      <c r="AR2" s="175"/>
+      <c r="AS2" s="174">
         <v>45558</v>
       </c>
-      <c r="AT2" s="172"/>
-      <c r="AU2" s="171">
+      <c r="AT2" s="175"/>
+      <c r="AU2" s="174">
         <v>45565</v>
       </c>
-      <c r="AV2" s="172"/>
-      <c r="AW2" s="187"/>
-      <c r="AX2" s="196"/>
+      <c r="AV2" s="175"/>
+      <c r="AW2" s="192"/>
+      <c r="AX2" s="180"/>
       <c r="AY2" s="106"/>
-      <c r="AZ2" s="201" t="s">
+      <c r="AZ2" s="185" t="s">
         <v>88</v>
       </c>
-      <c r="BA2" s="203" t="s">
+      <c r="BA2" s="187" t="s">
         <v>102</v>
       </c>
-      <c r="BB2" s="203" t="s">
+      <c r="BB2" s="187" t="s">
         <v>36</v>
       </c>
-      <c r="BC2" s="205" t="s">
+      <c r="BC2" s="189" t="s">
         <v>61</v>
       </c>
-      <c r="BD2" s="190"/>
-      <c r="BE2" s="189" t="s">
+      <c r="BD2" s="170"/>
+      <c r="BE2" s="169" t="s">
         <v>88</v>
       </c>
-      <c r="BF2" s="189" t="s">
+      <c r="BF2" s="169" t="s">
         <v>102</v>
       </c>
-      <c r="BG2" s="189" t="s">
+      <c r="BG2" s="169" t="s">
         <v>36</v>
       </c>
-      <c r="BH2" s="189" t="s">
+      <c r="BH2" s="169" t="s">
         <v>61</v>
       </c>
     </row>
-    <row r="3" spans="1:60" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="179"/>
-      <c r="B3" s="180"/>
-      <c r="C3" s="183"/>
-      <c r="D3" s="185"/>
+    <row r="3" spans="1:60" s="1" customFormat="1" ht="15.75" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="198"/>
+      <c r="B3" s="199"/>
+      <c r="C3" s="202"/>
+      <c r="D3" s="204"/>
       <c r="E3" s="50" t="s">
         <v>26</v>
       </c>
@@ -13506,20 +13506,20 @@
       <c r="AV3" s="51" t="s">
         <v>27</v>
       </c>
-      <c r="AW3" s="188"/>
-      <c r="AX3" s="197"/>
+      <c r="AW3" s="193"/>
+      <c r="AX3" s="181"/>
       <c r="AY3" s="106"/>
-      <c r="AZ3" s="202"/>
-      <c r="BA3" s="204"/>
-      <c r="BB3" s="204"/>
-      <c r="BC3" s="206"/>
-      <c r="BD3" s="191"/>
-      <c r="BE3" s="190"/>
-      <c r="BF3" s="190"/>
-      <c r="BG3" s="190"/>
-      <c r="BH3" s="190"/>
-    </row>
-    <row r="4" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="AZ3" s="186"/>
+      <c r="BA3" s="188"/>
+      <c r="BB3" s="188"/>
+      <c r="BC3" s="190"/>
+      <c r="BD3" s="171"/>
+      <c r="BE3" s="170"/>
+      <c r="BF3" s="170"/>
+      <c r="BG3" s="170"/>
+      <c r="BH3" s="170"/>
+    </row>
+    <row r="4" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="54" t="s">
         <v>99</v>
       </c>
@@ -13639,7 +13639,7 @@
         <v>19.833333333333332</v>
       </c>
     </row>
-    <row r="5" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="61" t="s">
         <v>9</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>19.555555555555557</v>
       </c>
     </row>
-    <row r="6" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="61" t="s">
         <v>9</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>19.5</v>
       </c>
     </row>
-    <row r="7" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="61" t="s">
         <v>4</v>
       </c>
@@ -14130,7 +14130,7 @@
         <v>19.333333333333332</v>
       </c>
     </row>
-    <row r="8" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="61" t="s">
         <v>7</v>
       </c>
@@ -14289,7 +14289,7 @@
         <v>19.25</v>
       </c>
     </row>
-    <row r="9" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="61" t="s">
         <v>20</v>
       </c>
@@ -14442,7 +14442,7 @@
         <v>18.142857142857142</v>
       </c>
     </row>
-    <row r="10" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="61" t="s">
         <v>5</v>
       </c>
@@ -14597,7 +14597,7 @@
         <v>18.142857142857142</v>
       </c>
     </row>
-    <row r="11" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="61" t="s">
         <v>22</v>
       </c>
@@ -14770,7 +14770,7 @@
         <v>17.375</v>
       </c>
     </row>
-    <row r="12" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="61" t="s">
         <v>19</v>
       </c>
@@ -14933,7 +14933,7 @@
         <v>16.285714285714285</v>
       </c>
     </row>
-    <row r="13" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="61" t="s">
         <v>15</v>
       </c>
@@ -15072,7 +15072,7 @@
         <v>18.600000000000001</v>
       </c>
     </row>
-    <row r="14" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="61" t="s">
         <v>2</v>
       </c>
@@ -15215,7 +15215,7 @@
         <v>17.75</v>
       </c>
     </row>
-    <row r="15" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="61" t="s">
         <v>17</v>
       </c>
@@ -15366,7 +15366,7 @@
         <v>16.2</v>
       </c>
     </row>
-    <row r="16" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A16" s="61" t="s">
         <v>121</v>
       </c>
@@ -15455,7 +15455,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A17" s="61" t="s">
         <v>13</v>
       </c>
@@ -15595,7 +15595,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A18" s="61" t="s">
         <v>71</v>
       </c>
@@ -15696,7 +15696,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A19" s="61" t="s">
         <v>11</v>
       </c>
@@ -15797,7 +15797,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:60" ht="15" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A20" s="81" t="s">
         <v>0</v>
       </c>
@@ -15911,7 +15911,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:60" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:60" ht="15" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A21" s="81" t="s">
         <v>25</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:60" s="104" customFormat="1" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:60" s="104" customFormat="1" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="101"/>
       <c r="B22" s="102"/>
       <c r="C22" s="102"/>
@@ -16133,7 +16133,7 @@
       </c>
       <c r="AY22" s="105"/>
     </row>
-    <row r="23" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:60" x14ac:dyDescent="0.2">
       <c r="C23" s="93"/>
       <c r="D23" s="94"/>
       <c r="E23" s="95"/>
@@ -16147,7 +16147,7 @@
       <c r="BC23" s="97"/>
       <c r="BD23" s="94"/>
     </row>
-    <row r="24" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:60" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D24" s="92" t="s">
         <v>28</v>
       </c>
@@ -16178,7 +16178,7 @@
       </c>
       <c r="AU24" s="117"/>
     </row>
-    <row r="25" spans="1:60" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:60" ht="16" thickBot="1" x14ac:dyDescent="0.25">
       <c r="D25" s="92" t="s">
         <v>29</v>
       </c>
@@ -16214,7 +16214,7 @@
       <c r="AW25" s="162"/>
       <c r="AX25" s="162"/>
     </row>
-    <row r="26" spans="1:60" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:60" x14ac:dyDescent="0.2">
       <c r="D26" s="92" t="s">
         <v>91</v>
       </c>
@@ -16257,6 +16257,50 @@
     <sortCondition ref="AX4:AX21"/>
   </sortState>
   <mergeCells count="60">
+    <mergeCell ref="M1:N1"/>
+    <mergeCell ref="O1:P1"/>
+    <mergeCell ref="E2:F2"/>
+    <mergeCell ref="AI1:AJ1"/>
+    <mergeCell ref="AI2:AJ2"/>
+    <mergeCell ref="AC1:AD1"/>
+    <mergeCell ref="AC2:AD2"/>
+    <mergeCell ref="AG2:AH2"/>
+    <mergeCell ref="Y2:Z2"/>
+    <mergeCell ref="Y1:Z1"/>
+    <mergeCell ref="W2:X2"/>
+    <mergeCell ref="W1:X1"/>
+    <mergeCell ref="K2:L2"/>
+    <mergeCell ref="M2:N2"/>
+    <mergeCell ref="AA1:AB1"/>
+    <mergeCell ref="AA2:AB2"/>
+    <mergeCell ref="A1:B3"/>
+    <mergeCell ref="C1:C3"/>
+    <mergeCell ref="D1:D3"/>
+    <mergeCell ref="E1:F1"/>
+    <mergeCell ref="U2:V2"/>
+    <mergeCell ref="G1:H1"/>
+    <mergeCell ref="S2:T2"/>
+    <mergeCell ref="S1:T1"/>
+    <mergeCell ref="Q2:R2"/>
+    <mergeCell ref="Q1:R1"/>
+    <mergeCell ref="I1:J1"/>
+    <mergeCell ref="O2:P2"/>
+    <mergeCell ref="K1:L1"/>
+    <mergeCell ref="U1:V1"/>
+    <mergeCell ref="G2:H2"/>
+    <mergeCell ref="I2:J2"/>
+    <mergeCell ref="AE1:AF1"/>
+    <mergeCell ref="AE2:AF2"/>
+    <mergeCell ref="AG1:AH1"/>
+    <mergeCell ref="AW1:AW3"/>
+    <mergeCell ref="AK1:AL1"/>
+    <mergeCell ref="AK2:AL2"/>
+    <mergeCell ref="AO1:AP1"/>
+    <mergeCell ref="AO2:AP2"/>
+    <mergeCell ref="AS1:AT1"/>
+    <mergeCell ref="AS2:AT2"/>
+    <mergeCell ref="AU1:AV1"/>
+    <mergeCell ref="AU2:AV2"/>
     <mergeCell ref="BD1:BD3"/>
     <mergeCell ref="AM1:AN1"/>
     <mergeCell ref="AM2:AN2"/>
@@ -16273,50 +16317,6 @@
     <mergeCell ref="BC2:BC3"/>
     <mergeCell ref="AQ1:AR1"/>
     <mergeCell ref="AQ2:AR2"/>
-    <mergeCell ref="AE1:AF1"/>
-    <mergeCell ref="AE2:AF2"/>
-    <mergeCell ref="AG1:AH1"/>
-    <mergeCell ref="AW1:AW3"/>
-    <mergeCell ref="AK1:AL1"/>
-    <mergeCell ref="AK2:AL2"/>
-    <mergeCell ref="AO1:AP1"/>
-    <mergeCell ref="AO2:AP2"/>
-    <mergeCell ref="AS1:AT1"/>
-    <mergeCell ref="AS2:AT2"/>
-    <mergeCell ref="AU1:AV1"/>
-    <mergeCell ref="AU2:AV2"/>
-    <mergeCell ref="A1:B3"/>
-    <mergeCell ref="C1:C3"/>
-    <mergeCell ref="D1:D3"/>
-    <mergeCell ref="E1:F1"/>
-    <mergeCell ref="U2:V2"/>
-    <mergeCell ref="G1:H1"/>
-    <mergeCell ref="S2:T2"/>
-    <mergeCell ref="S1:T1"/>
-    <mergeCell ref="Q2:R2"/>
-    <mergeCell ref="Q1:R1"/>
-    <mergeCell ref="I1:J1"/>
-    <mergeCell ref="O2:P2"/>
-    <mergeCell ref="K1:L1"/>
-    <mergeCell ref="U1:V1"/>
-    <mergeCell ref="G2:H2"/>
-    <mergeCell ref="I2:J2"/>
-    <mergeCell ref="M1:N1"/>
-    <mergeCell ref="O1:P1"/>
-    <mergeCell ref="E2:F2"/>
-    <mergeCell ref="AI1:AJ1"/>
-    <mergeCell ref="AI2:AJ2"/>
-    <mergeCell ref="AC1:AD1"/>
-    <mergeCell ref="AC2:AD2"/>
-    <mergeCell ref="AG2:AH2"/>
-    <mergeCell ref="Y2:Z2"/>
-    <mergeCell ref="Y1:Z1"/>
-    <mergeCell ref="W2:X2"/>
-    <mergeCell ref="W1:X1"/>
-    <mergeCell ref="K2:L2"/>
-    <mergeCell ref="M2:N2"/>
-    <mergeCell ref="AA1:AB1"/>
-    <mergeCell ref="AA2:AB2"/>
   </mergeCells>
   <phoneticPr fontId="18" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -16333,25 +16333,25 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D7815779-C5C7-4C22-8371-169A5BC8E021}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -16381,7 +16381,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -16411,7 +16411,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -16439,7 +16439,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -16499,7 +16499,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -16552,7 +16552,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -16600,7 +16600,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>54</v>
       </c>
@@ -16658,7 +16658,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -16720,7 +16720,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>55</v>
       </c>
@@ -16769,7 +16769,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -16823,7 +16823,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>62</v>
       </c>
@@ -16873,7 +16873,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -16928,7 +16928,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>66</v>
       </c>
@@ -16978,7 +16978,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -17033,7 +17033,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>63</v>
       </c>
@@ -17086,7 +17086,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -17144,7 +17144,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -17197,7 +17197,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -17255,7 +17255,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>53</v>
       </c>
@@ -17304,7 +17304,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -17358,7 +17358,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>64</v>
       </c>
@@ -17411,7 +17411,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -17469,7 +17469,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>56</v>
       </c>
@@ -17522,7 +17522,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -17580,7 +17580,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>52</v>
       </c>
@@ -17629,7 +17629,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -17698,25 +17698,25 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D1CEBE32-9D3C-479F-8090-DE2CE97DA990}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -17746,7 +17746,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -17776,7 +17776,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -17804,7 +17804,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -17864,7 +17864,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -17917,7 +17917,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -17965,7 +17965,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>52</v>
       </c>
@@ -18020,7 +18020,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -18082,7 +18082,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>55</v>
       </c>
@@ -18131,7 +18131,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -18185,7 +18185,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>62</v>
       </c>
@@ -18235,7 +18235,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -18290,7 +18290,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>66</v>
       </c>
@@ -18340,7 +18340,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -18395,7 +18395,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
@@ -18448,7 +18448,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -18506,7 +18506,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -18559,7 +18559,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -18617,7 +18617,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>63</v>
       </c>
@@ -18666,7 +18666,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -18720,7 +18720,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>67</v>
       </c>
@@ -18773,7 +18773,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -18831,7 +18831,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -18862,7 +18862,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17" t="str">
@@ -18920,7 +18920,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -18947,7 +18947,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17" t="str">
@@ -19016,25 +19016,25 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2D590E60-77C9-4B37-BD32-B5D113E70530}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -19064,7 +19064,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -19094,7 +19094,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -19122,7 +19122,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -19182,7 +19182,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -19235,7 +19235,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -19283,7 +19283,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>52</v>
       </c>
@@ -19338,7 +19338,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -19400,7 +19400,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>100</v>
       </c>
@@ -19449,7 +19449,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -19503,7 +19503,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>56</v>
       </c>
@@ -19553,7 +19553,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -19608,7 +19608,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>55</v>
       </c>
@@ -19658,7 +19658,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -19713,7 +19713,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>64</v>
       </c>
@@ -19766,7 +19766,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -19824,7 +19824,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>63</v>
       </c>
@@ -19877,7 +19877,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -19935,7 +19935,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>62</v>
       </c>
@@ -19984,7 +19984,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -20038,7 +20038,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>51</v>
       </c>
@@ -20091,7 +20091,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -20149,7 +20149,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -20180,7 +20180,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17" t="str">
@@ -20238,7 +20238,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -20265,7 +20265,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17" t="str">
@@ -20334,25 +20334,25 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{30184089-AC63-4F42-87E9-DFB789D392DB}">
   <dimension ref="A1:Z26"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -20382,7 +20382,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -20412,7 +20412,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -20440,7 +20440,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -20500,7 +20500,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -20553,7 +20553,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -20601,7 +20601,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>62</v>
       </c>
@@ -20656,7 +20656,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -20718,7 +20718,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>123</v>
       </c>
@@ -20764,7 +20764,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17"/>
@@ -20788,7 +20788,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>54</v>
       </c>
@@ -20838,7 +20838,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -20893,7 +20893,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>67</v>
       </c>
@@ -20943,7 +20943,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -20998,7 +20998,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>100</v>
       </c>
@@ -21051,7 +21051,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -21109,7 +21109,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>52</v>
       </c>
@@ -21162,7 +21162,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -21220,7 +21220,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>64</v>
       </c>
@@ -21269,7 +21269,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -21323,7 +21323,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>56</v>
       </c>
@@ -21376,7 +21376,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -21434,7 +21434,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>51</v>
       </c>
@@ -21487,7 +21487,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -21545,7 +21545,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -21572,7 +21572,7 @@
       <c r="R25" s="39"/>
       <c r="T25" s="3"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17" t="str">
@@ -21641,25 +21641,25 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AC67D2C9-51E9-4325-BE9D-6FFAA314D9FD}">
   <dimension ref="A1:Z20"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -21689,7 +21689,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -21719,7 +21719,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -21747,7 +21747,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -21807,7 +21807,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -21860,7 +21860,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -21908,7 +21908,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>66</v>
       </c>
@@ -21963,7 +21963,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -22025,7 +22025,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>63</v>
       </c>
@@ -22071,7 +22071,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -22125,7 +22125,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>55</v>
       </c>
@@ -22175,7 +22175,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -22230,7 +22230,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>100</v>
       </c>
@@ -22280,7 +22280,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -22335,7 +22335,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>52</v>
       </c>
@@ -22388,7 +22388,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -22446,7 +22446,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>51</v>
       </c>
@@ -22499,7 +22499,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -22557,7 +22557,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>67</v>
       </c>
@@ -22606,7 +22606,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -22675,25 +22675,25 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{18132F1E-B4D4-4DA6-B049-FBEAA451119B}">
   <dimension ref="A1:Z22"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.140625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" style="3" customWidth="1"/>
+    <col min="1" max="1" width="20.1640625" style="3" customWidth="1"/>
+    <col min="2" max="2" width="13.5" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="7.28515625" style="3" customWidth="1"/>
-    <col min="14" max="14" width="8.28515625" style="3" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="7.33203125" style="3" customWidth="1"/>
+    <col min="14" max="14" width="8.33203125" style="3" customWidth="1"/>
     <col min="15" max="15" width="17" style="3" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -22723,7 +22723,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -22753,7 +22753,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -22781,7 +22781,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -22841,7 +22841,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -22894,7 +22894,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -22942,7 +22942,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>54</v>
       </c>
@@ -22997,7 +22997,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -23059,7 +23059,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>56</v>
       </c>
@@ -23105,7 +23105,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -23159,7 +23159,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>66</v>
       </c>
@@ -23209,7 +23209,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -23264,7 +23264,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>53</v>
       </c>
@@ -23314,7 +23314,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -23369,7 +23369,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>51</v>
       </c>
@@ -23422,7 +23422,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -23480,7 +23480,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>62</v>
       </c>
@@ -23533,7 +23533,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -23591,7 +23591,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>63</v>
       </c>
@@ -23640,7 +23640,7 @@
       <c r="R19" s="39"/>
       <c r="T19" s="3"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -23694,7 +23694,7 @@
       <c r="R20" s="39"/>
       <c r="T20" s="3"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>67</v>
       </c>
@@ -23743,7 +23743,7 @@
       <c r="R21" s="39"/>
       <c r="T21" s="3"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -23812,20 +23812,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9E789909-84FC-488D-8D94-3FAD76B00BC6}">
   <dimension ref="A1:B1000"/>
-  <sheetFormatPr defaultColWidth="12.7109375" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="12.6640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="20.28515625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="22.85546875" style="3" customWidth="1"/>
-    <col min="3" max="26" width="7.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="12.7109375" style="3"/>
+    <col min="1" max="1" width="20.33203125" style="3" customWidth="1"/>
+    <col min="2" max="2" width="22.83203125" style="3" customWidth="1"/>
+    <col min="3" max="26" width="7.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="12.6640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A3" s="9" t="s">
         <v>58</v>
       </c>
@@ -23833,7 +23833,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A4" s="10">
         <v>-5</v>
       </c>
@@ -23841,7 +23841,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A5" s="10">
         <v>-4</v>
       </c>
@@ -23849,7 +23849,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A6" s="10">
         <v>-3</v>
       </c>
@@ -23857,7 +23857,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A7" s="10">
         <v>-2</v>
       </c>
@@ -23865,7 +23865,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A8" s="10">
         <v>-1</v>
       </c>
@@ -23873,7 +23873,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A9" s="10">
         <v>0</v>
       </c>
@@ -23881,7 +23881,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A10" s="10">
         <v>1</v>
       </c>
@@ -23889,7 +23889,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A11" s="10">
         <v>2</v>
       </c>
@@ -23897,7 +23897,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A12" s="10">
         <v>3</v>
       </c>
@@ -23905,7 +23905,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A13" s="10">
         <v>4</v>
       </c>
@@ -23913,7 +23913,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A14" s="10">
         <v>5</v>
       </c>
@@ -23921,7 +23921,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A15" s="10">
         <v>6</v>
       </c>
@@ -23929,996 +23929,996 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="18" spans="1:1" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:1" ht="14" x14ac:dyDescent="0.15">
       <c r="A18" s="11" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="21" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="22" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="23" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="24" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="25" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="26" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="27" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="28" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="29" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="31" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="32" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="33" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="34" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="35" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="36" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="37" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="38" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="39" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="40" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="41" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="42" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="43" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="44" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="45" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="46" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="47" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="48" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="49" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="50" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="51" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="52" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="53" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="54" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="55" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="56" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="57" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="58" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="59" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="60" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="61" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="62" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="63" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="64" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="65" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="66" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="67" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="68" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="69" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="70" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="71" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="72" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="73" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="74" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="75" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="76" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="77" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="78" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="79" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="80" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="81" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="82" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="83" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="84" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="85" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="86" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="87" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="88" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="89" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="90" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="91" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="92" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="93" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="94" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="95" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="96" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="97" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="98" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="99" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="100" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="101" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="102" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="103" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="104" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="105" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="106" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="107" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="108" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="109" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="110" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="111" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="112" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="113" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="114" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="115" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="116" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="117" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="118" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="119" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="120" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="121" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="122" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="123" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="124" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="125" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="126" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="127" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="128" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="129" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="130" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="131" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="132" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="133" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="134" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="135" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="136" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="137" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="138" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="139" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="140" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="141" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="142" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="143" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="144" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="145" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="146" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="147" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="148" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="149" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="150" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="151" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="152" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="153" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="154" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="155" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="156" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="157" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="158" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="159" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="160" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="161" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="162" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="163" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="164" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="165" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="166" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="167" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="168" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="169" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="170" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="171" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="172" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="173" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="174" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="175" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="176" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="177" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="178" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="179" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="180" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="181" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="182" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="183" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="184" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="185" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="186" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="187" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="188" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="189" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="190" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="191" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="192" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="193" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="194" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="195" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="196" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="197" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="198" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="199" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="200" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="201" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="202" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="203" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="204" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="205" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="206" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="207" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="208" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="209" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="210" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="211" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="212" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="213" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="214" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="215" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="216" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="217" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="218" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="219" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="220" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="221" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="222" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="223" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="224" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="225" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="226" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="227" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="228" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="229" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="230" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="231" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="232" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="233" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="234" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="235" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="236" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="237" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="238" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="239" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="240" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="241" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="242" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="243" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="244" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="245" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="246" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="247" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="248" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="249" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="250" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="251" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="252" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="253" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="254" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="255" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="256" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="257" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="258" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="259" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="260" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="261" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="262" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="263" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="264" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="265" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="266" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="267" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="268" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="269" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="270" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="271" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="272" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="273" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="274" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="275" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="276" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="277" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="278" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="279" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="280" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="281" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="282" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="283" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="284" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="285" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="286" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="287" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="288" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="289" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="290" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="291" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="292" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="293" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="294" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="295" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="296" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="297" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="298" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="299" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="300" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="301" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="302" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="303" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="304" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="305" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="306" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="307" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="308" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="309" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="310" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="311" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="312" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="313" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="314" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="315" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="316" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="317" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="318" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="319" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="320" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="321" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="322" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="323" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="324" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="325" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="326" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="327" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="328" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="329" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="330" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="331" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="332" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="333" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="334" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="335" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="336" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="337" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="338" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="339" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="340" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="341" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="342" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="343" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="344" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="345" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="346" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="347" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="348" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="349" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="350" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="351" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="352" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="353" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="354" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="355" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="356" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="357" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="358" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="359" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="360" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="361" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="362" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="363" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="364" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="365" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="366" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="367" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="368" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="369" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="370" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="371" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="372" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="373" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="374" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="375" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="376" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="377" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="378" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="379" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="380" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="381" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="382" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="383" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="384" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="385" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="386" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="387" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="388" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="389" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="390" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="391" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="392" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="393" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="394" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="395" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="396" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="397" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="398" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="399" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="400" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="401" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="402" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="403" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="404" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="405" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="406" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="407" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="408" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="409" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="410" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="411" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="412" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="413" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="414" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="415" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="416" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="417" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="418" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="419" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="420" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="421" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="422" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="423" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="424" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="425" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="426" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="427" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="428" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="429" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="430" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="431" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="432" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="433" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="434" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="435" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="436" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="437" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="438" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="439" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="440" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="441" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="442" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="443" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="444" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="445" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="446" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="447" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="448" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="449" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="450" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="451" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="452" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="453" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="454" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="455" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="456" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="457" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="458" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="459" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="460" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="461" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="462" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="463" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="464" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="465" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="466" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="467" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="468" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="469" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="470" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="471" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="472" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="473" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="474" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="475" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="476" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="477" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="478" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="479" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="480" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="481" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="482" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="483" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="484" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="485" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="486" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="487" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="488" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="489" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="490" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="491" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="492" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="493" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="494" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="495" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="496" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="497" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="498" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="499" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="500" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="501" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="502" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="503" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="504" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="505" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="506" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="507" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="508" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="509" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="510" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="511" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="512" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="513" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="514" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="515" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="516" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="517" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="518" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="519" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="520" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="521" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="522" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="523" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="524" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="525" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="526" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="527" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="528" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="529" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="530" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="531" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="532" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="533" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="534" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="535" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="536" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="537" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="538" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="539" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="540" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="541" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="542" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="543" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="544" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="545" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="546" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="547" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="548" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="549" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="550" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="551" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="552" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="553" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="554" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="555" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="556" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="557" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="558" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="559" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="560" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="561" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="562" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="563" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="564" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="565" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="566" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="567" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="568" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="569" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="570" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="571" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="572" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="573" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="574" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="575" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="576" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="577" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="578" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="579" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="580" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="581" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="582" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="583" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="584" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="585" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="586" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="587" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="588" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="589" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="590" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="591" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="592" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="593" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="594" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="595" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="596" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="597" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="598" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="599" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="600" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="601" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="602" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="603" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="604" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="605" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="606" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="607" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="608" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="609" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="610" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="611" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="612" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="613" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="614" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="615" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="616" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="617" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="618" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="619" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="620" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="621" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="622" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="623" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="624" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="625" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="626" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="627" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="628" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="629" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="630" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="631" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="632" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="633" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="634" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="635" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="636" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="637" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="638" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="639" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="640" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="641" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="642" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="643" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="644" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="645" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="646" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="647" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="648" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="649" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="650" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="651" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="652" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="653" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="654" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="655" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="656" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="657" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="658" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="659" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="660" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="661" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="662" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="663" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="664" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="665" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="666" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="667" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="668" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="669" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="670" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="671" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="672" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="673" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="674" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="675" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="676" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="677" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="678" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="679" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="680" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="681" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="682" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="683" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="684" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="685" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="686" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="687" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="688" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="689" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="690" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="691" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="692" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="693" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="694" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="695" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="696" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="697" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="698" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="699" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="700" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="701" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="702" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="703" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="704" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="705" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="706" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="707" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="708" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="709" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="710" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="711" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="712" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="713" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="714" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="715" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="716" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="717" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="718" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="719" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="720" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="721" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="722" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="723" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="724" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="725" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="726" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="727" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="728" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="729" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="730" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="731" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="732" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="733" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="734" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="735" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="736" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="737" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="738" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="739" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="740" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="741" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="742" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="743" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="744" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="745" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="746" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="747" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="748" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="749" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="750" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="751" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="752" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="753" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="754" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="755" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="756" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="757" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="758" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="759" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="760" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="761" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="762" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="763" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="764" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="765" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="766" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="767" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="768" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="769" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="770" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="771" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="772" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="773" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="774" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="775" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="776" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="777" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="778" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="779" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="780" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="781" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="782" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="783" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="784" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="785" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="786" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="787" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="788" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="789" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="790" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="791" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="792" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="793" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="794" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="795" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="796" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="797" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="798" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="799" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="800" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="801" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="802" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="803" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="804" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="805" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="806" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="807" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="808" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="809" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="810" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="811" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="812" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="813" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="814" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="815" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="816" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="817" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="818" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="819" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="820" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="821" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="822" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="823" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="824" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="825" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="826" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="827" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="828" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="829" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="830" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="831" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="832" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="833" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="834" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="835" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="836" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="837" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="838" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="839" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="840" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="841" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="842" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="843" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="844" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="845" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="846" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="847" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="848" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="849" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="850" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="851" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="852" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="853" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="854" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="855" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="856" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="857" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="858" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="859" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="860" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="861" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="862" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="863" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="864" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="865" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="866" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="867" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="868" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="869" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="870" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="871" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="872" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="873" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="874" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="875" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="876" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="877" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="878" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="879" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="880" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="881" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="882" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="883" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="884" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="885" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="886" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="887" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="888" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="889" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="890" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="891" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="892" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="893" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="894" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="895" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="896" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="897" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="898" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="899" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="900" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="901" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="902" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="903" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="904" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="905" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="906" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="907" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="908" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="909" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="910" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="911" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="912" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="913" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="914" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="915" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="916" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="917" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="918" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="919" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="920" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="921" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="922" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="923" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="924" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="925" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="926" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="927" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="928" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="929" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="930" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="931" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="932" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="933" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="934" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="935" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="936" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="937" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="938" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="939" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="940" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="941" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="942" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="943" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="944" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="945" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="946" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="947" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="948" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="949" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="950" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="951" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="952" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="953" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="954" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="955" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="956" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="957" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="958" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="961" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="962" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="963" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="964" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="965" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="966" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="967" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="968" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="969" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="970" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="971" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="972" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="973" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="974" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="975" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="976" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="977" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="978" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="979" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="980" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="981" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="982" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="983" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="984" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="985" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="986" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="987" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="988" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="989" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="990" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="991" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="992" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="993" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="994" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="995" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="996" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="997" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="998" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="999" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
+    <row r="1000" ht="15.75" customHeight="1" x14ac:dyDescent="0.15"/>
   </sheetData>
   <hyperlinks>
     <hyperlink ref="A18" r:id="rId1" xr:uid="{BB8AB8C5-9F96-41D8-B252-ACC21DAB1BB3}"/>
@@ -24931,20 +24931,20 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{299C7D47-E383-421C-AFFB-D42B2CA94D59}">
   <dimension ref="A1:Z28"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -24974,7 +24974,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" ht="15" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -25004,7 +25004,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -25032,7 +25032,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -25090,7 +25090,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -25141,7 +25141,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -25189,7 +25189,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -25247,7 +25247,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -25310,7 +25310,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -25366,7 +25366,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -25427,7 +25427,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>52</v>
       </c>
@@ -25483,7 +25483,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -25544,7 +25544,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>53</v>
       </c>
@@ -25600,7 +25600,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -25661,7 +25661,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
@@ -25717,7 +25717,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -25778,7 +25778,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>55</v>
       </c>
@@ -25834,7 +25834,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -25895,7 +25895,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
@@ -25951,7 +25951,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -26012,7 +26012,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>64</v>
       </c>
@@ -26068,7 +26068,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -26129,7 +26129,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>65</v>
       </c>
@@ -26185,7 +26185,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -26246,7 +26246,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>63</v>
       </c>
@@ -26302,7 +26302,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -26363,7 +26363,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>62</v>
       </c>
@@ -26419,7 +26419,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17">
@@ -26496,20 +26496,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6EE06649-6874-4A1D-B258-119905808454}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -26539,7 +26539,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -26569,7 +26569,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -26597,7 +26597,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -26655,7 +26655,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -26706,7 +26706,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -26754,7 +26754,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -26812,7 +26812,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -26875,7 +26875,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -26931,7 +26931,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -26992,7 +26992,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>52</v>
       </c>
@@ -27048,7 +27048,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -27109,7 +27109,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>53</v>
       </c>
@@ -27165,7 +27165,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -27226,7 +27226,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
@@ -27282,7 +27282,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -27343,7 +27343,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>55</v>
       </c>
@@ -27399,7 +27399,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -27460,7 +27460,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
@@ -27516,7 +27516,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -27577,7 +27577,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>64</v>
       </c>
@@ -27633,7 +27633,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -27694,7 +27694,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>65</v>
       </c>
@@ -27750,7 +27750,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -27811,7 +27811,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12" t="s">
         <v>62</v>
       </c>
@@ -27867,7 +27867,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -27928,7 +27928,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="12" t="s">
         <v>66</v>
       </c>
@@ -27984,7 +27984,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17">
@@ -28045,7 +28045,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:26" ht="14" x14ac:dyDescent="0.15">
       <c r="A29" s="3" t="s">
         <v>67</v>
       </c>
@@ -28088,7 +28088,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="30" spans="1:26" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" ht="14" x14ac:dyDescent="0.15">
       <c r="C30" s="3">
         <f>IF(C29&gt;0, VLOOKUP(C29-C$5-(INT($M29/9)+(MOD($M29,9)&gt;=C$6)), '[1]Point System'!$A$4:$B$15, 2),"")</f>
         <v>3</v>
@@ -28150,20 +28150,20 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51FF4A29-33E9-4DE5-AD7F-F973D4F3F862}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -28193,7 +28193,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -28223,7 +28223,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -28251,7 +28251,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -28309,7 +28309,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -28360,7 +28360,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -28408,7 +28408,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>50</v>
       </c>
@@ -28466,7 +28466,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -28529,7 +28529,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>51</v>
       </c>
@@ -28585,7 +28585,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -28646,7 +28646,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>52</v>
       </c>
@@ -28702,7 +28702,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -28763,7 +28763,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>53</v>
       </c>
@@ -28819,7 +28819,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -28880,7 +28880,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
@@ -28936,7 +28936,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -28997,7 +28997,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>55</v>
       </c>
@@ -29053,7 +29053,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -29114,7 +29114,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>56</v>
       </c>
@@ -29170,7 +29170,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -29231,7 +29231,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>63</v>
       </c>
@@ -29287,7 +29287,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -29348,7 +29348,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>67</v>
       </c>
@@ -29404,7 +29404,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -29465,7 +29465,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -29493,7 +29493,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -29521,7 +29521,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -29549,7 +29549,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -29577,8 +29577,8 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:26" ht="14.25" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:26" ht="14" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:26" ht="14" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
@@ -29595,20 +29595,20 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9F4DC545-13E9-47BC-BF7F-E64EA9119729}">
   <dimension ref="A1:Z30"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="7.85546875" style="3" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="7.83203125" style="3" customWidth="1"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -29638,7 +29638,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -29668,7 +29668,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -29696,7 +29696,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -29754,7 +29754,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -29805,7 +29805,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -29853,7 +29853,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="12" t="s">
         <v>51</v>
       </c>
@@ -29911,7 +29911,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -29974,7 +29974,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="12" t="s">
         <v>54</v>
       </c>
@@ -30030,7 +30030,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -30091,7 +30091,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="12" t="s">
         <v>55</v>
       </c>
@@ -30147,7 +30147,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -30208,7 +30208,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="12" t="s">
         <v>63</v>
       </c>
@@ -30264,7 +30264,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -30325,7 +30325,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>62</v>
       </c>
@@ -30381,7 +30381,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -30442,7 +30442,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>66</v>
       </c>
@@ -30498,7 +30498,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -30559,7 +30559,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>72</v>
       </c>
@@ -30615,7 +30615,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17" t="e">
@@ -30676,7 +30676,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>68</v>
       </c>
@@ -30732,7 +30732,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17" t="e">
@@ -30793,7 +30793,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12"/>
       <c r="B23" s="13"/>
       <c r="C23" s="13"/>
@@ -30821,7 +30821,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17"/>
@@ -30849,7 +30849,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="12"/>
       <c r="B25" s="13"/>
       <c r="C25" s="13"/>
@@ -30877,7 +30877,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17"/>
@@ -30905,7 +30905,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="12"/>
       <c r="B27" s="13"/>
       <c r="C27" s="13"/>
@@ -30933,7 +30933,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17"/>
@@ -30961,8 +30961,8 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="14.25" x14ac:dyDescent="0.2"/>
-    <row r="30" spans="1:26" ht="14.25" x14ac:dyDescent="0.2"/>
+    <row r="29" spans="1:26" ht="14" x14ac:dyDescent="0.15"/>
+    <row r="30" spans="1:26" ht="14" x14ac:dyDescent="0.15"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A1:O1"/>
@@ -30979,24 +30979,24 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC9BBB3-9887-4614-A221-B067C2A396F6}">
   <dimension ref="A1:Z31"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="9.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="9.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -31026,7 +31026,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -31056,7 +31056,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -31084,7 +31084,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -31142,7 +31142,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -31193,7 +31193,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -31241,7 +31241,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="31" t="s">
         <v>50</v>
       </c>
@@ -31299,7 +31299,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -31364,7 +31364,7 @@
       <c r="Y8" s="2"/>
       <c r="Z8" s="2"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="31" t="s">
         <v>51</v>
       </c>
@@ -31420,7 +31420,7 @@
       <c r="Y9" s="2"/>
       <c r="Z9" s="2"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -31489,7 +31489,7 @@
       <c r="Y10" s="2"/>
       <c r="Z10" s="2"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="31" t="s">
         <v>52</v>
       </c>
@@ -31553,7 +31553,7 @@
       <c r="Y11" s="2"/>
       <c r="Z11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="17">
@@ -31622,7 +31622,7 @@
       <c r="Y12" s="2"/>
       <c r="Z12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="31" t="s">
         <v>53</v>
       </c>
@@ -31686,7 +31686,7 @@
       <c r="Y13" s="2"/>
       <c r="Z13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="29">
@@ -31755,7 +31755,7 @@
       <c r="Y14" s="2"/>
       <c r="Z14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="12" t="s">
         <v>54</v>
       </c>
@@ -31813,7 +31813,7 @@
       <c r="Y15" s="2"/>
       <c r="Z15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -31873,7 +31873,7 @@
       <c r="Y16" s="2"/>
       <c r="Z16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="12" t="s">
         <v>55</v>
       </c>
@@ -31929,7 +31929,7 @@
       <c r="Y17" s="2"/>
       <c r="Z17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -31989,7 +31989,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="31" t="s">
         <v>56</v>
       </c>
@@ -32041,7 +32041,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -32098,7 +32098,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="12" t="s">
         <v>64</v>
       </c>
@@ -32150,7 +32150,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -32207,7 +32207,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="12" t="s">
         <v>65</v>
       </c>
@@ -32259,7 +32259,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -32317,7 +32317,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="31" t="s">
         <v>62</v>
       </c>
@@ -32373,7 +32373,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -32434,7 +32434,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="31" t="s">
         <v>67</v>
       </c>
@@ -32490,7 +32490,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17">
@@ -32551,13 +32551,13 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" x14ac:dyDescent="0.2">
       <c r="Q29" s="2"/>
       <c r="R29" s="2"/>
       <c r="S29" s="2"/>
       <c r="T29" s="39"/>
     </row>
-    <row r="30" spans="1:26" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:26" ht="14" x14ac:dyDescent="0.15">
       <c r="C30" s="30" t="s">
         <v>79</v>
       </c>
@@ -32586,7 +32586,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:26" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E31" s="34">
         <v>3</v>
       </c>
@@ -32620,25 +32620,25 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5F873C6-3826-4D67-A96A-087AA522689D}">
   <dimension ref="A1:Z33"/>
-  <sheetFormatPr defaultColWidth="14.140625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="14.1640625" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="14.140625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="14.1640625" style="3" customWidth="1"/>
     <col min="3" max="11" width="5" style="3" customWidth="1"/>
-    <col min="12" max="12" width="5.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="6.140625" style="3" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="5.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="6.1640625" style="3" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="5" style="3" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.140625" style="3" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="8.7109375" style="3" customWidth="1"/>
-    <col min="17" max="17" width="15.140625" style="3" customWidth="1"/>
-    <col min="18" max="18" width="13.7109375" style="3" customWidth="1"/>
-    <col min="19" max="19" width="8.7109375" style="3" customWidth="1"/>
-    <col min="20" max="20" width="8.7109375" style="42" customWidth="1"/>
-    <col min="21" max="26" width="8.7109375" style="3" customWidth="1"/>
-    <col min="27" max="16384" width="14.140625" style="3"/>
+    <col min="15" max="15" width="14.1640625" style="3" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="8.6640625" style="3" customWidth="1"/>
+    <col min="17" max="17" width="15.1640625" style="3" customWidth="1"/>
+    <col min="18" max="18" width="13.6640625" style="3" customWidth="1"/>
+    <col min="19" max="19" width="8.6640625" style="3" customWidth="1"/>
+    <col min="20" max="20" width="8.6640625" style="42" customWidth="1"/>
+    <col min="21" max="26" width="8.6640625" style="3" customWidth="1"/>
+    <col min="27" max="16384" width="14.1640625" style="3"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="26.25" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:26" ht="26" x14ac:dyDescent="0.3">
       <c r="A1" s="166" t="s">
         <v>41</v>
       </c>
@@ -32668,7 +32668,7 @@
       <c r="Y1" s="2"/>
       <c r="Z1" s="2"/>
     </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:26" x14ac:dyDescent="0.2">
       <c r="A2" s="168" t="s">
         <v>42</v>
       </c>
@@ -32698,7 +32698,7 @@
       <c r="Y2" s="2"/>
       <c r="Z2" s="2"/>
     </row>
-    <row r="3" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="4"/>
       <c r="B3" s="2"/>
       <c r="C3" s="5"/>
@@ -32726,7 +32726,7 @@
       <c r="Y3" s="2"/>
       <c r="Z3" s="2"/>
     </row>
-    <row r="4" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A4" s="20" t="s">
         <v>43</v>
       </c>
@@ -32788,7 +32788,7 @@
       <c r="Y4" s="4"/>
       <c r="Z4" s="4"/>
     </row>
-    <row r="5" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A5" s="23"/>
       <c r="B5" s="7" t="s">
         <v>49</v>
@@ -32844,7 +32844,7 @@
       <c r="Y5" s="4"/>
       <c r="Z5" s="4"/>
     </row>
-    <row r="6" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A6" s="25"/>
       <c r="B6" s="26" t="s">
         <v>74</v>
@@ -32892,7 +32892,7 @@
       <c r="Y6" s="4"/>
       <c r="Z6" s="4"/>
     </row>
-    <row r="7" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A7" s="43" t="s">
         <v>50</v>
       </c>
@@ -32950,7 +32950,7 @@
       <c r="Y7" s="2"/>
       <c r="Z7" s="2"/>
     </row>
-    <row r="8" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A8" s="16"/>
       <c r="B8" s="17" t="s">
         <v>75</v>
@@ -33017,7 +33017,7 @@
       <c r="X8" s="2"/>
       <c r="Z8" s="47"/>
     </row>
-    <row r="9" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A9" s="43" t="s">
         <v>66</v>
       </c>
@@ -33066,7 +33066,7 @@
       <c r="R9" s="39"/>
       <c r="T9" s="3"/>
     </row>
-    <row r="10" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A10" s="16"/>
       <c r="B10" s="17"/>
       <c r="C10" s="17">
@@ -33120,7 +33120,7 @@
       <c r="R10" s="39"/>
       <c r="T10" s="3"/>
     </row>
-    <row r="11" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A11" s="43" t="s">
         <v>52</v>
       </c>
@@ -33170,7 +33170,7 @@
       <c r="S11" s="2"/>
       <c r="T11" s="2"/>
     </row>
-    <row r="12" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A12" s="16"/>
       <c r="B12" s="17"/>
       <c r="C12" s="35">
@@ -33230,7 +33230,7 @@
       <c r="S12" s="2"/>
       <c r="T12" s="2"/>
     </row>
-    <row r="13" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A13" s="43" t="s">
         <v>53</v>
       </c>
@@ -33280,7 +33280,7 @@
       <c r="S13" s="2"/>
       <c r="T13" s="2"/>
     </row>
-    <row r="14" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A14" s="16"/>
       <c r="B14" s="17"/>
       <c r="C14" s="17">
@@ -33335,7 +33335,7 @@
       <c r="S14" s="2"/>
       <c r="T14" s="2"/>
     </row>
-    <row r="15" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A15" s="43" t="s">
         <v>54</v>
       </c>
@@ -33385,7 +33385,7 @@
       <c r="S15" s="2"/>
       <c r="T15" s="2"/>
     </row>
-    <row r="16" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A16" s="16"/>
       <c r="B16" s="17"/>
       <c r="C16" s="17">
@@ -33445,7 +33445,7 @@
       <c r="S16" s="2"/>
       <c r="T16" s="2"/>
     </row>
-    <row r="17" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A17" s="43" t="s">
         <v>63</v>
       </c>
@@ -33495,7 +33495,7 @@
       <c r="S17" s="2"/>
       <c r="T17" s="2"/>
     </row>
-    <row r="18" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A18" s="16"/>
       <c r="B18" s="17"/>
       <c r="C18" s="17">
@@ -33555,7 +33555,7 @@
       <c r="Y18" s="2"/>
       <c r="Z18" s="2"/>
     </row>
-    <row r="19" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A19" s="12" t="s">
         <v>55</v>
       </c>
@@ -33611,7 +33611,7 @@
       <c r="Y19" s="2"/>
       <c r="Z19" s="2"/>
     </row>
-    <row r="20" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A20" s="16"/>
       <c r="B20" s="17"/>
       <c r="C20" s="17">
@@ -33671,7 +33671,7 @@
       <c r="Y20" s="2"/>
       <c r="Z20" s="2"/>
     </row>
-    <row r="21" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A21" s="43" t="s">
         <v>56</v>
       </c>
@@ -33724,7 +33724,7 @@
       <c r="Y21" s="2"/>
       <c r="Z21" s="2"/>
     </row>
-    <row r="22" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A22" s="16"/>
       <c r="B22" s="17"/>
       <c r="C22" s="17">
@@ -33782,7 +33782,7 @@
       <c r="Y22" s="2"/>
       <c r="Z22" s="2"/>
     </row>
-    <row r="23" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A23" s="43" t="s">
         <v>64</v>
       </c>
@@ -33835,7 +33835,7 @@
       <c r="Y23" s="2"/>
       <c r="Z23" s="2"/>
     </row>
-    <row r="24" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A24" s="16"/>
       <c r="B24" s="17"/>
       <c r="C24" s="17">
@@ -33898,7 +33898,7 @@
       <c r="Y24" s="2"/>
       <c r="Z24" s="2"/>
     </row>
-    <row r="25" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A25" s="43" t="s">
         <v>65</v>
       </c>
@@ -33950,7 +33950,7 @@
       <c r="Y25" s="2"/>
       <c r="Z25" s="2"/>
     </row>
-    <row r="26" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A26" s="16"/>
       <c r="B26" s="17"/>
       <c r="C26" s="17">
@@ -34008,7 +34008,7 @@
       <c r="Y26" s="2"/>
       <c r="Z26" s="2"/>
     </row>
-    <row r="27" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A27" s="43" t="s">
         <v>62</v>
       </c>
@@ -34064,7 +34064,7 @@
       <c r="Y27" s="2"/>
       <c r="Z27" s="2"/>
     </row>
-    <row r="28" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A28" s="16"/>
       <c r="B28" s="17"/>
       <c r="C28" s="17">
@@ -34125,7 +34125,7 @@
       <c r="Y28" s="2"/>
       <c r="Z28" s="2"/>
     </row>
-    <row r="29" spans="1:26" ht="18.75" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:26" ht="19" x14ac:dyDescent="0.2">
       <c r="A29" s="43" t="s">
         <v>67</v>
       </c>
@@ -34181,7 +34181,7 @@
       <c r="Y29" s="2"/>
       <c r="Z29" s="2"/>
     </row>
-    <row r="30" spans="1:26" ht="19.5" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:26" ht="20" thickBot="1" x14ac:dyDescent="0.25">
       <c r="A30" s="16"/>
       <c r="B30" s="17"/>
       <c r="C30" s="17">
@@ -34245,13 +34245,13 @@
       <c r="Y30" s="2"/>
       <c r="Z30" s="2"/>
     </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:26" x14ac:dyDescent="0.2">
       <c r="Q31" s="2"/>
       <c r="R31" s="2"/>
       <c r="S31" s="2"/>
       <c r="T31" s="39"/>
     </row>
-    <row r="32" spans="1:26" ht="14.25" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:26" ht="14" x14ac:dyDescent="0.15">
       <c r="C32" s="30"/>
       <c r="D32" s="30"/>
       <c r="E32" s="30"/>
@@ -34264,7 +34264,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="33" spans="5:11" ht="15" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="33" spans="5:11" ht="15" customHeight="1" x14ac:dyDescent="0.15">
       <c r="E33" s="34"/>
       <c r="G33" s="34"/>
       <c r="H33" s="34"/>
